--- a/data/trans_bre/IP16B06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Provincia-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-27,08</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-27,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1224,100 +1224,19 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-27,08</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-27,08%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-78,5; 0,0</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-78,5; 0,0</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>

--- a/data/trans_bre/IP16B06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Provincia-trans_bre.xlsx
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
